--- a/0_1_Output_Data/5_ifo_qoq_error_series_matched_to_ifoCAST_since_2022/ifo_qoq_matched_errors_first_since_2022.xlsx
+++ b/0_1_Output_Data/5_ifo_qoq_error_series_matched_to_ifoCAST_since_2022/ifo_qoq_matched_errors_first_since_2022.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Q0</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>2025-08-22 00:00:00_diff</t>
+  </si>
+  <si>
+    <t>2025-11-25 00:00:00_diff</t>
   </si>
 </sst>
 </file>
@@ -446,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -838,6 +841,11 @@
         <v>0.0959495356205764</v>
       </c>
     </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
